--- a/dataset/construct/dataset_splits/data_size/50_percent/tum/fold4.xlsx
+++ b/dataset/construct/dataset_splits/data_size/50_percent/tum/fold4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>702</v>
+        <v>355</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,88 +625,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>79.79584759297281</v>
+        <v>93.53169315790809</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>24.0344071512902</v>
       </c>
       <c r="E2" t="n">
-        <v>22.3863142771225</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="I2" t="n">
-        <v>2220</v>
+        <v>104</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>184</v>
       </c>
       <c r="K2" t="n">
-        <v>692</v>
+        <v>429</v>
       </c>
       <c r="L2" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>166</v>
       </c>
-      <c r="N2" t="n">
-        <v>1449</v>
-      </c>
       <c r="O2" t="n">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="P2" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>133</v>
+        <v>40</v>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="T2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V2" t="n">
-        <v>47</v>
+        <v>0.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X2" t="n">
-        <v>24.6</v>
+        <v>22.9276988327862</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.267605633802817</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.4647313470843</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>24.8459903311873</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -730,33 +715,24 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>116</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>704</v>
+        <v>336</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,80 +740,82 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85.76208647045399</v>
+        <v>83.0155395213831</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>19.7231833910034</v>
       </c>
       <c r="E3" t="n">
-        <v>24.609375</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>652</v>
+      </c>
+      <c r="I3" t="n">
+        <v>918</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>547</v>
       </c>
       <c r="K3" t="n">
-        <v>514.4</v>
+        <v>2117</v>
       </c>
       <c r="L3" t="n">
-        <v>174.8</v>
+        <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>420.7</v>
+        <v>157</v>
       </c>
       <c r="N3" t="n">
-        <v>1109.9</v>
+        <v>92</v>
       </c>
       <c r="O3" t="n">
-        <v>5.4</v>
+        <v>344</v>
       </c>
       <c r="P3" t="n">
-        <v>13.8</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="n">
-        <v>68.09999999999999</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
-        <v>87.3</v>
+        <v>88</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>5.7</v>
+        <v>26.4</v>
       </c>
       <c r="V3" t="n">
-        <v>5.7</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>27.0562770562771</v>
       </c>
       <c r="X3" t="n">
-        <v>22.85</v>
+        <v>26.6741965227618</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.319852941176471</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.7140310669722</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.9332496617824</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -846,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -855,28 +833,21 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>146</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>186</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>512</v>
+        <v>323</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,121 +855,114 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85.7615408015819</v>
+        <v>79.7188668339798</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>28.0403781445281</v>
       </c>
       <c r="E4" t="n">
-        <v>25.9106843468983</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="I4" t="n">
-        <v>8040</v>
+        <v>137.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="K4" t="n">
-        <v>248</v>
+        <v>431.7</v>
       </c>
       <c r="L4" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>615</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X4" t="n">
-        <v>22.8</v>
+        <v>21.406057760656</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.323529411764706</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.554876496053</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.7045529015462</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>140</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>485</v>
+        <v>1312</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1006,79 +970,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>89.0005646817248</v>
+        <v>77.89833593175651</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20.6575400021007</v>
       </c>
       <c r="E5" t="n">
-        <v>22.0385674931129</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>253.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4370</v>
+        <v>78.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>126.2</v>
       </c>
       <c r="K5" t="n">
-        <v>510</v>
+        <v>458.9</v>
       </c>
       <c r="L5" t="n">
-        <v>296</v>
+        <v>26.8</v>
       </c>
       <c r="M5" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1165</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>35</v>
+        <v>102.9</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>205</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>232</v>
+        <v>22.3</v>
       </c>
       <c r="V5" t="n">
-        <v>246</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>22.886427298192</v>
       </c>
       <c r="X5" t="n">
-        <v>22.05</v>
+        <v>22.5272697980512</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.221774193548387</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.5999490705373</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.1655797488585</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1093,34 +1057,27 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1419</v>
+        <v>796</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1128,41 +1085,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>77.95573351585671</v>
+        <v>77.90669860825921</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>28.125</v>
       </c>
       <c r="E6" t="n">
-        <v>33.0578512396694</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>58.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>34.8</v>
+      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>31.7</v>
+        <v>159.1</v>
       </c>
       <c r="L6" t="n">
-        <v>38.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>82.5</v>
+        <v>16.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1177,28 +1136,28 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>22.15</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>21.9314998726763</v>
       </c>
       <c r="X6" t="n">
-        <v>20.35</v>
+        <v>21.5128218033123</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.222707423580786</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.6582633053221</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3326250911699</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1213,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1225,24 +1184,15 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>180</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>556</v>
+        <v>659</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1250,88 +1200,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>78.32835766978479</v>
+        <v>87.6369685907674</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>22.7244034844085</v>
       </c>
       <c r="E7" t="n">
-        <v>25.8264462809917</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="I7" t="n">
-        <v>2310</v>
+        <v>127</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="K7" t="n">
-        <v>855</v>
+        <v>379</v>
       </c>
       <c r="L7" t="n">
-        <v>523</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1835</v>
+        <v>13</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>15</v>
+        <v>26.4</v>
       </c>
       <c r="V7" t="n">
-        <v>15</v>
+        <v>0.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X7" t="n">
-        <v>24.95</v>
+        <v>25.7021303318567</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.308474576271186</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>26.1013496307614</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>24.9992044677091</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1340,33 +1290,22 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>184</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>495</v>
+        <v>597</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1374,123 +1313,112 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>74.7334821722818</v>
+        <v>80.8852175070348</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>24.9680097375237</v>
       </c>
       <c r="E8" t="n">
-        <v>30.1102788964582</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>532</v>
       </c>
       <c r="I8" t="n">
-        <v>461</v>
+        <v>615</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>593</v>
       </c>
       <c r="K8" t="n">
-        <v>575</v>
+        <v>1740</v>
       </c>
       <c r="L8" t="n">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1072</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="P8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>0.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>28.6478227654698</v>
       </c>
       <c r="X8" t="n">
-        <v>24.35</v>
+        <v>27.9784080907002</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.15530303030303</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.7726133940886</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>148</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>637</v>
+        <v>505</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1498,88 +1426,88 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.3184899992395</v>
+        <v>76.737962962963</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>21.8775510204081</v>
       </c>
       <c r="E9" t="n">
-        <v>29.0123456790123</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>609</v>
       </c>
       <c r="I9" t="n">
-        <v>2930</v>
+        <v>576</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="K9" t="n">
-        <v>627</v>
+        <v>1543</v>
       </c>
       <c r="L9" t="n">
-        <v>283</v>
+        <v>203</v>
       </c>
       <c r="M9" t="n">
-        <v>214</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>1124</v>
+        <v>26</v>
       </c>
       <c r="O9" t="n">
-        <v>11</v>
+        <v>239</v>
       </c>
       <c r="P9" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="T9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>53</v>
+        <v>26.5</v>
       </c>
       <c r="V9" t="n">
-        <v>66</v>
+        <v>0.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>26.7379679144385</v>
       </c>
       <c r="X9" t="n">
-        <v>27.55</v>
+        <v>26.2896834807734</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.205211726384365</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>27.4734240347507</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1597,22 +1525,15 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>106</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>134</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>487</v>
+        <v>746</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1620,79 +1541,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>86.317406900398</v>
+        <v>77.1758883121657</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>33.203125</v>
       </c>
       <c r="E10" t="n">
-        <v>16.5051903114186</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>323</v>
       </c>
       <c r="I10" t="n">
-        <v>6570</v>
+        <v>172</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="K10" t="n">
-        <v>772</v>
+        <v>638</v>
       </c>
       <c r="L10" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
-        <v>244</v>
+        <v>14</v>
       </c>
       <c r="N10" t="n">
-        <v>1166</v>
+        <v>14</v>
       </c>
       <c r="O10" t="n">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>24</v>
+        <v>20.65</v>
       </c>
       <c r="V10" t="n">
-        <v>182</v>
+        <v>0.22</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>21.0720651897123</v>
       </c>
       <c r="X10" t="n">
-        <v>25.45</v>
+        <v>20.7723337439364</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.32013201320132</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>27.1836007130125</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>26.0709028381822</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1719,24 +1640,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>954</v>
+        <v>1345</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1744,82 +1656,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>78.7770593771389</v>
+        <v>77.4494138971278</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>24.3374797187669</v>
       </c>
       <c r="E11" t="n">
-        <v>28.2283864654296</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>55</v>
+        <v>40.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1580</v>
+        <v>36.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="K11" t="n">
-        <v>488</v>
+        <v>84.5</v>
       </c>
       <c r="L11" t="n">
-        <v>578</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1452</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>111</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>36</v>
+        <v>23.7</v>
       </c>
       <c r="V11" t="n">
-        <v>92</v>
+        <v>0.21</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>23.8413547237077</v>
       </c>
       <c r="X11" t="n">
-        <v>23.05</v>
+        <v>23.506086798771</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.19921875</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.8163986665956</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1828,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1840,27 +1752,16 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN11" t="n">
         <v>164</v>
       </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>941</v>
+        <v>983</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1868,85 +1769,85 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72.25305355920599</v>
+        <v>74.1668630694349</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>25.4580659041199</v>
       </c>
       <c r="E12" t="n">
-        <v>20.8325296091971</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>60</v>
+        <v>993</v>
       </c>
       <c r="I12" t="n">
-        <v>209</v>
+        <v>491</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>960</v>
       </c>
       <c r="K12" t="n">
-        <v>877</v>
+        <v>2444</v>
       </c>
       <c r="L12" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="M12" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>1071</v>
+        <v>43</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X12" t="n">
-        <v>23.9</v>
+        <v>23.6921643870788</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.249084249084249</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>24.1914947797301</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>23.5574721962474</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -1955,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -1964,27 +1865,18 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>188</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1109</v>
+        <v>693</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1992,88 +1884,88 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>79.1909800174918</v>
+        <v>77.651817628717</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>19.6623076682999</v>
       </c>
       <c r="E13" t="n">
-        <v>28.3937263385613</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>24</v>
+        <v>709</v>
       </c>
       <c r="I13" t="n">
-        <v>2490</v>
+        <v>417</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="K13" t="n">
-        <v>187</v>
+        <v>1573</v>
       </c>
       <c r="L13" t="n">
-        <v>173</v>
+        <v>48</v>
       </c>
       <c r="M13" t="n">
-        <v>158</v>
+        <v>25</v>
       </c>
       <c r="N13" t="n">
-        <v>518</v>
+        <v>166</v>
       </c>
       <c r="O13" t="n">
-        <v>24</v>
+        <v>239</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>33</v>
+        <v>25.1</v>
       </c>
       <c r="V13" t="n">
-        <v>33</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>25.7830404889228</v>
       </c>
       <c r="X13" t="n">
-        <v>30</v>
+        <v>24.8203626912254</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.208955223880597</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>30.2393684746626</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>29.7425256555005</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2091,24 +1983,13 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>180</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1079</v>
+        <v>2158</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2116,91 +1997,91 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>88.0231582249601</v>
+        <v>88.0696089056202</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>29.3877551020408</v>
       </c>
       <c r="E14" t="n">
-        <v>24.2809753428405</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>60</v>
+        <v>157.2</v>
       </c>
       <c r="I14" t="n">
-        <v>928</v>
+        <v>177.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>280.7</v>
       </c>
       <c r="K14" t="n">
-        <v>800</v>
+        <v>615.3</v>
       </c>
       <c r="L14" t="n">
-        <v>544</v>
+        <v>64.2</v>
       </c>
       <c r="M14" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1783</v>
+        <v>52.8</v>
       </c>
       <c r="O14" t="n">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="P14" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>98</v>
+        <v>22.6</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>28.615991851286</v>
       </c>
       <c r="X14" t="n">
-        <v>23.3</v>
+        <v>27.2921406849679</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.299270072992701</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.050433101168</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2209,30 +2090,19 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>170</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>671</v>
+        <v>348</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2240,88 +2110,88 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>76.85509126169291</v>
+        <v>88.94842941161561</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>22.5878330942278</v>
       </c>
       <c r="E15" t="n">
-        <v>23.9868703446534</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="I15" t="n">
-        <v>277</v>
+        <v>107</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="K15" t="n">
-        <v>488</v>
+        <v>557</v>
       </c>
       <c r="L15" t="n">
-        <v>262</v>
+        <v>26</v>
       </c>
       <c r="M15" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1039</v>
+        <v>260</v>
       </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>286</v>
       </c>
       <c r="P15" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>0.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X15" t="n">
-        <v>26.65</v>
+        <v>23.0660688205498</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.199324324324324</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>26.4196587726</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>25.8994624442976</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2330,33 +2200,22 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>188</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>530</v>
+        <v>637</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2364,121 +2223,112 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>84.5046505437676</v>
+        <v>80.3184899992395</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>29.0123456790123</v>
       </c>
       <c r="E16" t="n">
-        <v>24.3374797187669</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>627</v>
       </c>
       <c r="I16" t="n">
-        <v>2040</v>
+        <v>283</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="K16" t="n">
-        <v>455</v>
+        <v>1124</v>
       </c>
       <c r="L16" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="N16" t="n">
-        <v>589</v>
+        <v>75</v>
       </c>
       <c r="O16" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>27.55</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>0.21</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X16" t="n">
-        <v>23.3</v>
+        <v>27.4734240347507</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.193798449612403</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>23.176170013362</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN16" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>966</v>
+        <v>561</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2486,79 +2336,79 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>78.7858618526124</v>
+        <v>82.85644725834661</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>24.6530314097881</v>
       </c>
       <c r="E17" t="n">
-        <v>23.3354661447551</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="I17" t="n">
-        <v>366</v>
+        <v>233</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="K17" t="n">
-        <v>304.8</v>
+        <v>747</v>
       </c>
       <c r="L17" t="n">
-        <v>168.7</v>
+        <v>115</v>
       </c>
       <c r="M17" t="n">
-        <v>105.7</v>
+        <v>110</v>
       </c>
       <c r="N17" t="n">
-        <v>579.2</v>
+        <v>164</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="P17" t="n">
-        <v>10.7</v>
+        <v>25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R17" t="n">
-        <v>10.7</v>
+        <v>106</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>21.8678380443086</v>
       </c>
       <c r="X17" t="n">
-        <v>25.1</v>
+        <v>20.6802165106906</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.232394366197183</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.2419149477973</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>24.7201610353049</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2573,36 +2423,27 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>672</v>
+        <v>588</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2610,91 +2451,91 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>84.077751159784</v>
+        <v>86.977426040003</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>30.7173999207292</v>
       </c>
       <c r="E18" t="n">
-        <v>23.3234180638182</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>556</v>
       </c>
       <c r="I18" t="n">
-        <v>5030</v>
+        <v>582</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="K18" t="n">
-        <v>701.4</v>
+        <v>1456</v>
       </c>
       <c r="L18" t="n">
-        <v>213.8</v>
+        <v>91</v>
       </c>
       <c r="M18" t="n">
-        <v>169.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1085</v>
+        <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>35.9</v>
+        <v>136</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q18" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>69.2</v>
+        <v>20</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>6.9</v>
+        <v>26.65</v>
       </c>
       <c r="V18" t="n">
-        <v>6.9</v>
+        <v>0.18</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>27.2472625413802</v>
       </c>
       <c r="X18" t="n">
-        <v>23.75</v>
+        <v>26.8406888888731</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.220973782771536</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>24.3188184364655</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>23.7002215763568</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2703,30 +2544,21 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>170</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>754</v>
+        <v>2375</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2734,88 +2566,88 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>65.49301657920751</v>
+        <v>85.331470485715</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>23.4567901234567</v>
       </c>
       <c r="E19" t="n">
-        <v>31.2100121719047</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>38.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>121.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1730</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>197.3</v>
       </c>
       <c r="K19" t="n">
-        <v>283</v>
+        <v>388.1</v>
       </c>
       <c r="L19" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>284</v>
+        <v>5.4</v>
       </c>
       <c r="N19" t="n">
-        <v>776</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>14.6</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>44</v>
+        <v>24.25</v>
       </c>
       <c r="V19" t="n">
-        <v>44</v>
+        <v>0.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>24.7326203208556</v>
       </c>
       <c r="X19" t="n">
-        <v>23.4</v>
+        <v>24.3805715703063</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.279411764705882</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8163986665956</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2824,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -2833,24 +2665,13 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN19" t="n">
         <v>142</v>
       </c>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>365</v>
+        <v>592</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2858,119 +2679,110 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>86.5307742033615</v>
+        <v>81.5341052551525</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>26.8687356599444</v>
       </c>
       <c r="E20" t="n">
-        <v>30.4878048780487</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>484</v>
+      </c>
+      <c r="I20" t="n">
+        <v>784</v>
+      </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>419</v>
       </c>
       <c r="K20" t="n">
-        <v>145</v>
+        <v>1687</v>
       </c>
       <c r="L20" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="N20" t="n">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>28.9661319073084</v>
       </c>
       <c r="X20" t="n">
-        <v>22.25</v>
+        <v>28.2049576036652</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.301526717557252</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.2816399286988</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.4950646217447</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN20" t="inlineStr"/>
+        <v>230</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2217</v>
+        <v>959</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2978,77 +2790,79 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>82.77436832965751</v>
+        <v>75.6452314814815</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>19.9510204081632</v>
       </c>
       <c r="E21" t="n">
-        <v>20.6131310030261</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>45</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>281</v>
+      </c>
+      <c r="I21" t="n">
+        <v>78</v>
+      </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>348.5</v>
+        <v>394</v>
       </c>
       <c r="L21" t="n">
-        <v>31.1</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>518.6</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>205.1</v>
+        <v>15</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>283.8</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>109.1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>170.5</v>
+        <v>22.4</v>
       </c>
       <c r="V21" t="n">
-        <v>279.6</v>
+        <v>0.28</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X21" t="n">
-        <v>23.75</v>
+        <v>22.6203056614775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.297491039426523</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>24.0005092946269</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>23.39481796886</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3063,36 +2877,25 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>158</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>254</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="AK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1664</v>
+        <v>1726</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3100,119 +2903,114 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>77.41136002104091</v>
+        <v>71.1663767840393</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>28.8888888888888</v>
       </c>
       <c r="E22" t="n">
-        <v>31.5334467120181</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>60</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="I22" t="n">
+        <v>88</v>
+      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="K22" t="n">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="L22" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>763</v>
+        <v>7.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>123</v>
+        <v>6.5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>153</v>
+        <v>26.85</v>
       </c>
       <c r="V22" t="n">
-        <v>153</v>
+        <v>0.23</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>27.0562770562771</v>
       </c>
       <c r="X22" t="n">
-        <v>21.7</v>
+        <v>26.5306572035833</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.298039215686275</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2816399286988</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.789128418268</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN22" t="inlineStr"/>
+        <v>162</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2683</v>
+        <v>471</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3220,123 +3018,114 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>84.3759558711689</v>
+        <v>75.0402101553984</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>24.2105958514995</v>
       </c>
       <c r="E23" t="n">
-        <v>29.9687825182101</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>464</v>
       </c>
       <c r="I23" t="n">
-        <v>419</v>
+        <v>640</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="K23" t="n">
-        <v>302</v>
+        <v>1824</v>
       </c>
       <c r="L23" t="n">
-        <v>228</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>706</v>
+        <v>99</v>
       </c>
       <c r="O23" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W23" t="n">
+        <v>25.6557168321874</v>
+      </c>
+      <c r="X23" t="n">
+        <v>24.7175864208069</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>85</v>
       </c>
-      <c r="R23" t="n">
-        <v>204</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>71</v>
-      </c>
-      <c r="V23" t="n">
-        <v>74</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>23.1729055258467</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>22.4905136383469</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
       <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>72</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>133</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2192</v>
+        <v>2482</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3344,41 +3133,43 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>83.62327093948841</v>
+        <v>78.8975567850534</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>27.7176852352623</v>
       </c>
       <c r="E24" t="n">
-        <v>26.9896193771626</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>314.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>160.8</v>
+      </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>322.6</v>
       </c>
       <c r="K24" t="n">
-        <v>80.7</v>
+        <v>797.6</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M24" t="n">
-        <v>32.9</v>
+        <v>13.9</v>
       </c>
       <c r="N24" t="n">
-        <v>113.6</v>
+        <v>25.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>50.8</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -3393,43 +3184,43 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>23.25</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>23.3638910109498</v>
       </c>
       <c r="X24" t="n">
-        <v>21.6</v>
+        <v>22.8665507818143</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.357414448669202</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.6768525592055</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.6555825335006</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -3441,22 +3232,13 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN24" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="AK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>620</v>
+        <v>544</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3464,79 +3246,79 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>85.82740633001239</v>
+        <v>86.9331313534616</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>29.5525494276795</v>
       </c>
       <c r="E25" t="n">
-        <v>29.0659268067115</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>60</v>
+        <v>256</v>
       </c>
       <c r="I25" t="n">
-        <v>728</v>
+        <v>186</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K25" t="n">
-        <v>1675</v>
+        <v>476</v>
       </c>
       <c r="L25" t="n">
-        <v>1134</v>
+        <v>75</v>
       </c>
       <c r="M25" t="n">
-        <v>1007</v>
+        <v>15</v>
       </c>
       <c r="N25" t="n">
-        <v>3816</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>371</v>
+        <v>90</v>
       </c>
       <c r="P25" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>191</v>
+        <v>21.75</v>
       </c>
       <c r="V25" t="n">
-        <v>358</v>
+        <v>0.31</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>22.7591036414566</v>
       </c>
       <c r="X25" t="n">
-        <v>26.4</v>
+        <v>21.3763064498772</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.160278745644599</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>26.3138801572997</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3563,24 +3345,15 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>230</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1776</v>
+        <v>2246</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3588,86 +3361,88 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>82.5145346604305</v>
+        <v>76.92898734377771</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>22.7244034844085</v>
       </c>
       <c r="E26" t="n">
-        <v>22.9130330700044</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>225.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>178.6</v>
+      </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>267.7</v>
       </c>
       <c r="K26" t="n">
-        <v>742.3</v>
+        <v>671.5999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>555.2</v>
+        <v>25.6</v>
       </c>
       <c r="M26" t="n">
-        <v>535.8</v>
+        <v>90.3</v>
       </c>
       <c r="N26" t="n">
-        <v>1833.3</v>
+        <v>96</v>
       </c>
       <c r="O26" t="n">
-        <v>22.7</v>
+        <v>211.9</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>174.3</v>
+        <v>54.7</v>
       </c>
       <c r="R26" t="n">
-        <v>197</v>
+        <v>63.1</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>117.8</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>147.7</v>
+        <v>24.5</v>
       </c>
       <c r="V26" t="n">
-        <v>147.7</v>
+        <v>0.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>24.6052966641202</v>
       </c>
       <c r="X26" t="n">
-        <v>25.85</v>
+        <v>23.9831715115263</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.179577464788732</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>26.0058568882098</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>25.6872693127872</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3676,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -3685,24 +3460,15 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>248</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>520</v>
+        <v>621</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3710,117 +3476,110 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>91.96256179177119</v>
+        <v>90.7882052817705</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>28.734672057202</v>
       </c>
       <c r="E27" t="n">
-        <v>24.4646016033723</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>31</v>
+        <v>596</v>
       </c>
       <c r="I27" t="n">
-        <v>17300</v>
+        <v>430</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="K27" t="n">
-        <v>503</v>
+        <v>1410</v>
       </c>
       <c r="L27" t="n">
-        <v>648</v>
+        <v>76</v>
       </c>
       <c r="M27" t="n">
-        <v>259</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
-        <v>1410</v>
+        <v>84</v>
       </c>
       <c r="O27" t="n">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>152</v>
+        <v>26.4</v>
       </c>
       <c r="V27" t="n">
-        <v>152</v>
+        <v>0.22</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>26.4196587726</v>
       </c>
       <c r="X27" t="n">
-        <v>23.95</v>
+        <v>25.8994624442976</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.270758122743682</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.9831467948561</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>105</v>
-      </c>
-      <c r="AN27" t="inlineStr"/>
+        <v>214</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
